--- a/Employee_Reports_wi52/Ryan Mauring Adol Q0444.xlsx
+++ b/Employee_Reports_wi52/Ryan Mauring Adol Q0444.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -753,11 +753,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -790,11 +790,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -827,11 +827,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>724</v>
+        <v>716</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -913,11 +913,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -962,11 +962,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1011,11 +1011,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1060,11 +1060,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1158,11 +1158,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1207,11 +1207,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1256,11 +1256,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1305,11 +1305,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1354,11 +1354,11 @@
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1403,11 +1403,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1452,11 +1452,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1501,11 +1501,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1550,11 +1550,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1599,11 +1599,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1648,11 +1648,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1698,11 +1698,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1747,11 +1747,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1784,11 +1784,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1833,11 +1833,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-151</v>
+        <v>-159</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1882,11 +1882,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1931,11 +1931,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-152</v>
+        <v>-160</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -1980,11 +1980,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-137</v>
+        <v>-145</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2029,11 +2029,11 @@
         </is>
       </c>
       <c r="H34" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2078,11 +2078,11 @@
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
@@ -2127,11 +2127,11 @@
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
@@ -2176,11 +2176,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="n">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -2213,11 +2213,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>-25</v>
+        <v>-33</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2250,11 +2250,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -2299,11 +2299,11 @@
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
@@ -2348,11 +2348,11 @@
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>-4</v>
+        <v>-12</v>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
@@ -2397,11 +2397,11 @@
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>-93</v>
+        <v>-101</v>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
@@ -2446,11 +2446,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="H44" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -2520,11 +2520,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -2569,11 +2569,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -2618,11 +2618,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -2667,11 +2667,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -2704,11 +2704,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -2741,11 +2741,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -2778,11 +2778,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -2815,11 +2815,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -2852,11 +2852,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7911</v>
+        <v>7903</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7994</v>
+        <v>7986</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3656,21 +3656,21 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ews 10 ft</t>
+          <t>stacker crane</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>24-Jun-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>19-May-2048</t>
+          <t>12-Jul-2048</t>
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7943</v>
+        <v>7989</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -3685,21 +3685,21 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>uld hoist</t>
+          <t>cs hoist</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>03-Aug-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>28-Jun-2048</t>
+          <t>12-Jul-2048</t>
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7983</v>
+        <v>7989</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>turntable</t>
+          <t>h9tv</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>28-Jul-2026</t>
+          <t>17-Aug-2026</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>22-Jun-2048</t>
+          <t>12-Jul-2048</t>
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7977</v>
+        <v>7989</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -3743,21 +3743,21 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>tilting deck</t>
+          <t>ews 10 ft</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>28-Jul-2026</t>
+          <t>24-Jun-2026</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>22-Jun-2048</t>
+          <t>19-May-2048</t>
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7977</v>
+        <v>7935</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>fmc deck</t>
+          <t>uld hoist</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>20-Jun-2026</t>
+          <t>03-Aug-2026</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>15-May-2048</t>
+          <t>28-Jun-2048</t>
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7939</v>
+        <v>7975</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -3801,21 +3801,21 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>powered roller deckmatarsop</t>
+          <t>turntable</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>24-Jul-2026</t>
+          <t>28-Jul-2026</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>18-Jun-2048</t>
+          <t>22-Jun-2048</t>
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7973</v>
+        <v>7969</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -3830,21 +3830,21 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>non powered roller deckmatarsop</t>
+          <t>tilting deck</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>25-Jul-2026</t>
+          <t>28-Jul-2026</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>19-Jun-2048</t>
+          <t>22-Jun-2048</t>
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7974</v>
+        <v>7969</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -3859,21 +3859,21 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>ball deck</t>
+          <t>fmc deck</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>19-Jun-2026</t>
+          <t>20-Jun-2026</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>14-May-2048</t>
+          <t>15-May-2048</t>
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7938</v>
+        <v>7931</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -3888,28 +3888,173 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>24-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>18-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>7965</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>non powered roller deckmatarsop</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>25-Jul-2026</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>19-Jun-2048</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>7966</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>cs placing deck</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2048</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>cs input and output conveyor</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>17-Aug-2026</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2048</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>7989</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>ball deck</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>19-Jun-2026</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>14-May-2048</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>7930</v>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>floor scale</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>26-Jun-2026</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>21-May-2048</t>
         </is>
       </c>
-      <c r="E11" s="3" t="n">
-        <v>7945</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="n"/>
+      <c r="E16" s="3" t="n">
+        <v>7937</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
